--- a/models/Extra/WACC_calculation/calculations_PSCC.xlsx
+++ b/models/Extra/WACC_calculation/calculations_PSCC.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\msc-thesis-incomplete-markets-LDES\models\Extra\WACC_calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5696A58C-1D9B-4538-8B2B-989231363142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533B5F09-F0AF-4171-8F1A-137EFBC11A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{96383EBD-4DDB-4AF0-82D8-D5946F1DED23}"/>
+    <workbookView xWindow="10812" yWindow="0" windowWidth="12324" windowHeight="12336" xr2:uid="{96383EBD-4DDB-4AF0-82D8-D5946F1DED23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
   <si>
     <t>Storage Duration</t>
   </si>
@@ -62,9 +62,6 @@
     <t>Complete</t>
   </si>
   <si>
-    <t>Fully Incomplete</t>
-  </si>
-  <si>
     <t>H2 P</t>
   </si>
   <si>
@@ -87,14 +84,36 @@
   </si>
   <si>
     <t>WACC (%)</t>
+  </si>
+  <si>
+    <t>incomplete</t>
+  </si>
+  <si>
+    <t>complete</t>
+  </si>
+  <si>
+    <t>risk  neutral</t>
+  </si>
+  <si>
+    <t>average price</t>
+  </si>
+  <si>
+    <t>UE</t>
+  </si>
+  <si>
+    <t>total energy</t>
+  </si>
+  <si>
+    <t>sw</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="174" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -154,8 +173,36 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" textRotation="90"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -165,39 +212,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -225,8 +249,8 @@
       <xdr:rowOff>134577</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>535305</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>24316</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
@@ -581,13 +605,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6432F40-47FA-41FE-B3BA-B8FF160E7C28}">
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -744,375 +768,955 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3" t="s">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6" t="s">
+      <c r="A15" s="20"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="18">
+      <c r="A16" s="2"/>
+      <c r="B16" s="7">
         <v>1</v>
       </c>
-      <c r="C16" s="15">
+      <c r="C16" s="4">
         <v>9.2314561119885408</v>
       </c>
-      <c r="D16" s="15">
+      <c r="D16" s="4">
         <v>1460.25304563908</v>
       </c>
-      <c r="E16" s="15">
+      <c r="E16" s="4">
         <f>0.55*D16/C16</f>
         <v>87.00027009373828</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="4">
         <v>9.8537635561804109</v>
       </c>
-      <c r="G16" s="15">
+      <c r="G16" s="4">
         <v>149.94818631989801</v>
       </c>
-      <c r="H16" s="15">
+      <c r="H16" s="4">
         <f>0.92*G16/F16</f>
         <v>13.999963630929692</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="19">
+      <c r="B17" s="8">
         <v>0.75</v>
       </c>
-      <c r="C17" s="22">
+      <c r="C17" s="5">
         <v>9.3123144036190499</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="5">
         <v>1471.1911719918801</v>
       </c>
-      <c r="E17" s="16">
+      <c r="E17" s="5">
         <f t="shared" ref="E17:E22" si="1">0.55*D17/C17</f>
         <v>86.890874762676802</v>
       </c>
-      <c r="F17" s="22">
+      <c r="F17" s="5">
         <v>9.9170011458535807</v>
       </c>
-      <c r="G17" s="22">
+      <c r="G17" s="5">
         <v>150.87044870158601</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="5">
         <f t="shared" ref="H17:H22" si="2">0.92*G17/F17</f>
         <v>13.996248539659941</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13"/>
-      <c r="B18" s="20">
+      <c r="A18" s="12"/>
+      <c r="B18" s="9">
         <v>0.5</v>
       </c>
-      <c r="C18" s="22">
+      <c r="C18" s="5">
         <v>9.3192296573445201</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="5">
         <v>1476.3692990195</v>
       </c>
-      <c r="E18" s="16">
+      <c r="E18" s="5">
         <f t="shared" si="1"/>
         <v>87.131999566163969</v>
       </c>
-      <c r="F18" s="22">
+      <c r="F18" s="5">
         <v>9.9223271791546601</v>
       </c>
-      <c r="G18" s="22">
+      <c r="G18" s="5">
         <v>150.959171161098</v>
       </c>
-      <c r="H18" s="16">
+      <c r="H18" s="5">
         <f t="shared" si="2"/>
         <v>13.996962099776511</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="21">
+      <c r="A19" s="13"/>
+      <c r="B19" s="10">
         <v>0.25</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="6">
         <v>9.3596951986104209</v>
       </c>
-      <c r="D19" s="17">
+      <c r="D19" s="6">
         <v>1515.44410403708</v>
       </c>
-      <c r="E19" s="17">
+      <c r="E19" s="6">
         <f t="shared" si="1"/>
         <v>89.051431647489764</v>
       </c>
-      <c r="F19" s="17">
+      <c r="F19" s="6">
         <v>9.9751365104761707</v>
       </c>
-      <c r="G19" s="17">
+      <c r="G19" s="6">
         <v>151.69309640894201</v>
       </c>
-      <c r="H19" s="17">
+      <c r="H19" s="6">
         <f t="shared" si="2"/>
         <v>13.990550259603893</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="19">
+      <c r="A20" s="11"/>
+      <c r="B20" s="8">
         <v>0.75</v>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="5">
         <v>9.0449880500000006</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="5">
         <v>1445.464076</v>
       </c>
-      <c r="E20" s="16">
+      <c r="E20" s="5">
         <f t="shared" si="1"/>
         <v>87.894559661690209</v>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="5">
         <v>9.8334867960000008</v>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="5">
         <v>149.6400165</v>
       </c>
-      <c r="H20" s="16">
+      <c r="H20" s="5">
         <f>0.92*G20/F20</f>
         <v>14.000000003660958</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="13"/>
-      <c r="B21" s="20">
+      <c r="A21" s="12"/>
+      <c r="B21" s="9">
         <v>0.5</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="5">
         <v>8.8987913150000004</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="5">
         <v>1480.1191269999999</v>
       </c>
-      <c r="E21" s="16">
+      <c r="E21" s="5">
         <f t="shared" si="1"/>
         <v>91.480459652738801</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="5">
         <v>9.8412435489999996</v>
       </c>
-      <c r="G21" s="22">
+      <c r="G21" s="5">
         <v>149.75805399999999</v>
       </c>
-      <c r="H21" s="16">
+      <c r="H21" s="5">
         <f t="shared" si="2"/>
         <v>13.999999999390322</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="14"/>
-      <c r="B22" s="21">
+      <c r="A22" s="13"/>
+      <c r="B22" s="10">
         <v>0.25</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="6">
         <v>9.0974252450000002</v>
       </c>
-      <c r="D22" s="17">
+      <c r="D22" s="6">
         <v>1540.5785550000001</v>
       </c>
-      <c r="E22" s="17">
+      <c r="E22" s="6">
         <f t="shared" si="1"/>
         <v>93.13824323158812</v>
       </c>
-      <c r="F22" s="17">
+      <c r="F22" s="6">
         <v>9.7426232650000006</v>
       </c>
-      <c r="G22" s="17">
+      <c r="G22" s="6">
         <v>148.25731049999999</v>
       </c>
-      <c r="H22" s="17">
+      <c r="H22" s="6">
         <f t="shared" si="2"/>
         <v>13.99999999486791</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="6" t="s">
+      <c r="A25" s="17"/>
+      <c r="B25" s="17"/>
+      <c r="C25" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C26" s="3">
+        <v>8.27</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A27" s="15"/>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27">
+        <v>9.58</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A28" s="15"/>
+      <c r="B28" t="s">
+        <v>10</v>
+      </c>
+      <c r="C28">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A29" s="16"/>
+      <c r="B29" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="1">
+        <v>6.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A30" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="3">
+        <v>9.8800000000000008</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A31" s="15"/>
+      <c r="B31" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A32" s="15"/>
+      <c r="B32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32">
+        <v>7.9</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="16"/>
+      <c r="B33" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="1">
+        <v>8.16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="3">
+        <v>11.87</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="15"/>
+      <c r="B35" t="s">
+        <v>9</v>
+      </c>
+      <c r="C35">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="15"/>
+      <c r="B36" t="s">
+        <v>10</v>
+      </c>
+      <c r="C36">
+        <v>8.6300000000000008</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="16"/>
+      <c r="B37" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="1">
+        <v>9.7899999999999991</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B42" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="C42" s="22"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B43" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D43" t="s">
+        <v>21</v>
+      </c>
+      <c r="F43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>1</v>
+      </c>
+      <c r="B44">
+        <v>139.87909999999999</v>
+      </c>
+      <c r="C44">
+        <v>12.1145660954987</v>
+      </c>
+      <c r="D44">
+        <v>570458.22547739302</v>
+      </c>
+      <c r="E44">
+        <f>C44*100/D44</f>
+        <v>2.1236552572031931E-3</v>
+      </c>
+      <c r="F44">
+        <v>10923247265.1402</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B46" s="22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C46" s="22"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B47" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>0.9</v>
+      </c>
+      <c r="B48">
+        <v>136.1422</v>
+      </c>
+      <c r="C48">
+        <v>11.5</v>
+      </c>
+      <c r="D48">
+        <v>10922995152.261499</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>0.8</v>
+      </c>
+      <c r="B49">
+        <v>132.75450000000001</v>
+      </c>
+      <c r="C49">
+        <v>10.852166783584</v>
+      </c>
+      <c r="D49">
+        <v>10922782112.403</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>0.7</v>
+      </c>
+      <c r="B50">
+        <v>129.62289999999999</v>
+      </c>
+      <c r="C50">
+        <v>10.999738686105299</v>
+      </c>
+      <c r="D50">
+        <v>10922560710.6152</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>0.6</v>
+      </c>
+      <c r="B51">
+        <v>126.5853</v>
+      </c>
+      <c r="C51">
+        <v>11.1627588333989</v>
+      </c>
+      <c r="D51">
+        <v>10922302339.0436</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>123.7778</v>
+      </c>
+      <c r="C52">
+        <v>11.9354764380048</v>
+      </c>
+      <c r="D52">
+        <v>10922081012.8708</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>0.4</v>
+      </c>
+      <c r="B53">
+        <v>121.2859</v>
+      </c>
+      <c r="C53">
+        <v>11.5517069497647</v>
+      </c>
+      <c r="D53">
+        <v>10921883049.368</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>0.3</v>
+      </c>
+      <c r="B54">
+        <v>119.10339999999999</v>
+      </c>
+      <c r="C54">
+        <v>13.1692941664275</v>
+      </c>
+      <c r="D54">
+        <v>10921628803.5324</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>0.2</v>
+      </c>
+      <c r="B55">
+        <v>117.13509999999999</v>
+      </c>
+      <c r="C55">
+        <v>15.911137879066599</v>
+      </c>
+      <c r="D55">
+        <v>10921355167.3988</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>0.1</v>
+      </c>
+      <c r="B56">
+        <v>115.93170000000001</v>
+      </c>
+      <c r="C56">
+        <v>20.691522848169999</v>
+      </c>
+      <c r="D56">
+        <v>10921045378.714899</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B58" s="22" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="8">
-        <v>8.27</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="4">
-        <v>9.58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="4">
-        <v>6.95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="6">
-        <v>6.96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="8">
-        <v>9.8800000000000008</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="10"/>
-      <c r="B31" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C31" s="4">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="10"/>
-      <c r="B32" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="4">
-        <v>7.9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C33" s="6">
-        <v>8.16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A34" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="8">
-        <v>11.87</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A35" s="10"/>
-      <c r="B35" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C35" s="4">
-        <v>11.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A36" s="10"/>
-      <c r="B36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="4">
-        <v>8.6300000000000008</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C37" s="6">
-        <v>9.7899999999999991</v>
+      <c r="C58" s="22"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B59" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>0.9</v>
+      </c>
+      <c r="B60">
+        <v>144.49359999999999</v>
+      </c>
+      <c r="C60">
+        <v>12.2</v>
+      </c>
+      <c r="D60">
+        <v>10923116520.682899</v>
+      </c>
+      <c r="E60">
+        <f>C48-C60</f>
+        <v>-0.69999999999999929</v>
+      </c>
+      <c r="F60" s="23">
+        <f>E60*100/$D$44</f>
+        <v>-1.2270837175048149E-4</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>0.8</v>
+      </c>
+      <c r="B61">
+        <v>149.56790000000001</v>
+      </c>
+      <c r="C61">
+        <v>12.344589826999099</v>
+      </c>
+      <c r="D61">
+        <v>10922863407.857</v>
+      </c>
+      <c r="E61">
+        <f t="shared" ref="E61:E68" si="3">C49-C61</f>
+        <v>-1.4924230434150996</v>
+      </c>
+      <c r="F61">
+        <f t="shared" ref="F61:F68" si="4">E61*100/$D$44</f>
+        <v>-2.6161828802909312E-4</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>0.7</v>
+      </c>
+      <c r="B62">
+        <v>155.08150000000001</v>
+      </c>
+      <c r="C62">
+        <v>12.881285057667901</v>
+      </c>
+      <c r="D62">
+        <v>10922574936.178499</v>
+      </c>
+      <c r="E62">
+        <f t="shared" si="3"/>
+        <v>-1.8815463715626013</v>
+      </c>
+      <c r="F62">
+        <f t="shared" si="4"/>
+        <v>-3.2983070232496211E-4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>0.6</v>
+      </c>
+      <c r="B63">
+        <v>161.34030000000001</v>
+      </c>
+      <c r="C63">
+        <v>13.429691243944699</v>
+      </c>
+      <c r="D63">
+        <v>10922238614.9389</v>
+      </c>
+      <c r="E63">
+        <f t="shared" si="3"/>
+        <v>-2.2669324105457989</v>
+      </c>
+      <c r="F63">
+        <f t="shared" si="4"/>
+        <v>-3.9738797852352753E-4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>0.5</v>
+      </c>
+      <c r="B64">
+        <v>168.96770000000001</v>
+      </c>
+      <c r="C64">
+        <v>16.099853951052499</v>
+      </c>
+      <c r="D64">
+        <v>10921849032.7728</v>
+      </c>
+      <c r="E64">
+        <f t="shared" si="3"/>
+        <v>-4.1643775130476985</v>
+      </c>
+      <c r="F64">
+        <f t="shared" si="4"/>
+        <v>-7.3000569140057583E-4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>0.4</v>
+      </c>
+      <c r="B65">
+        <v>180.73429999999999</v>
+      </c>
+      <c r="C65">
+        <v>16.7075652480851</v>
+      </c>
+      <c r="D65">
+        <v>10921849032.7728</v>
+      </c>
+      <c r="E65">
+        <f t="shared" si="3"/>
+        <v>-5.1558582983203998</v>
+      </c>
+      <c r="F65">
+        <f t="shared" si="4"/>
+        <v>-9.0380996680443587E-4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>0.3</v>
+      </c>
+      <c r="B66">
+        <v>199.27760000000001</v>
+      </c>
+      <c r="C66">
+        <v>18.642101199517601</v>
+      </c>
+      <c r="D66">
+        <v>10920737182.047899</v>
+      </c>
+      <c r="E66">
+        <f t="shared" si="3"/>
+        <v>-5.4728070330901009</v>
+      </c>
+      <c r="F66">
+        <f t="shared" si="4"/>
+        <v>-9.5937034276438618E-4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>0.2</v>
+      </c>
+      <c r="B67">
+        <v>223.67840000000001</v>
+      </c>
+      <c r="C67">
+        <v>21.611071151669599</v>
+      </c>
+      <c r="D67">
+        <v>10919868341.0651</v>
+      </c>
+      <c r="E67">
+        <f t="shared" si="3"/>
+        <v>-5.6999332726029994</v>
+      </c>
+      <c r="F67">
+        <f t="shared" si="4"/>
+        <v>-9.9918504423929721E-4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>0.1</v>
+      </c>
+      <c r="B68">
+        <v>305.96269999999998</v>
+      </c>
+      <c r="C68">
+        <v>38.503650886550403</v>
+      </c>
+      <c r="D68">
+        <v>10916415280.4674</v>
+      </c>
+      <c r="E68">
+        <f t="shared" si="3"/>
+        <v>-17.812128038380404</v>
+      </c>
+      <c r="F68">
+        <f t="shared" si="4"/>
+        <v>-3.1224246128582277E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D70">
+        <f>D48-D60</f>
+        <v>-121368.42140007019</v>
+      </c>
+      <c r="E70" s="9">
+        <f>D70+122500</f>
+        <v>1131.5785999298096</v>
+      </c>
+      <c r="F70">
+        <f>E60*100/$C$44</f>
+        <v>-5.7781681529649829</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D71">
+        <f>D49-D61</f>
+        <v>-81295.454000473022</v>
+      </c>
+      <c r="E71" s="9">
+        <f>D71+90000</f>
+        <v>8704.5459995269775</v>
+      </c>
+      <c r="F71">
+        <f t="shared" ref="F71:F79" si="5">E61*100/$C$44</f>
+        <v>-12.319244714588876</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D72">
+        <f>D50-D62</f>
+        <v>-14225.563299179077</v>
+      </c>
+      <c r="E72" s="9">
+        <f>D72+40000</f>
+        <v>25774.436700820923</v>
+      </c>
+      <c r="F72">
+        <f t="shared" si="5"/>
+        <v>-15.531273317842645</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D73">
+        <f>D51-D63</f>
+        <v>63724.104700088501</v>
+      </c>
+      <c r="E73" s="9">
+        <f t="shared" ref="E71:E78" si="6">D73</f>
+        <v>63724.104700088501</v>
+      </c>
+      <c r="F73">
+        <f t="shared" si="5"/>
+        <v>-18.712452370771267</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D74">
+        <f>D52-D64</f>
+        <v>231980.09799957275</v>
+      </c>
+      <c r="E74" s="9">
+        <f t="shared" si="6"/>
+        <v>231980.09799957275</v>
+      </c>
+      <c r="F74">
+        <f t="shared" si="5"/>
+        <v>-34.374962175451074</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D75">
+        <f>D53-D65</f>
+        <v>34016.595199584961</v>
+      </c>
+      <c r="E75" s="9">
+        <f>D75*10</f>
+        <v>340165.95199584961</v>
+      </c>
+      <c r="F75">
+        <f t="shared" si="5"/>
+        <v>-42.559166029364562</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D76">
+        <f>D54-D66</f>
+        <v>891621.48450088501</v>
+      </c>
+      <c r="E76" s="9">
+        <f t="shared" si="6"/>
+        <v>891621.48450088501</v>
+      </c>
+      <c r="F76">
+        <f t="shared" si="5"/>
+        <v>-45.175427579891462</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D77">
+        <f>D55-D67</f>
+        <v>1486826.3337001801</v>
+      </c>
+      <c r="E77" s="9">
+        <f t="shared" si="6"/>
+        <v>1486826.3337001801</v>
+      </c>
+      <c r="F77">
+        <f t="shared" si="5"/>
+        <v>-47.050247013971649</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="D78">
+        <f>D56-D68</f>
+        <v>4630098.2474994659</v>
+      </c>
+      <c r="E78" s="9">
+        <f t="shared" si="6"/>
+        <v>4630098.2474994659</v>
+      </c>
+      <c r="F78">
+        <f t="shared" si="5"/>
+        <v>-147.03067281129196</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E80">
+        <f>E70*100/$F$44</f>
+        <v>1.03593608426412E-5</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E81">
+        <f t="shared" ref="E81:E89" si="7">E71*100/$F$44</f>
+        <v>7.9688262915242678E-5</v>
+      </c>
+    </row>
+    <row r="82" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E82">
+        <f t="shared" si="7"/>
+        <v>2.3595947317860252E-4</v>
+      </c>
+    </row>
+    <row r="83" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E83">
+        <f t="shared" si="7"/>
+        <v>5.8338059327333745E-4</v>
+      </c>
+    </row>
+    <row r="84" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E84">
+        <f t="shared" si="7"/>
+        <v>2.1237283416617346E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E85">
+        <f t="shared" si="7"/>
+        <v>3.114146771001284E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E86">
+        <f t="shared" si="7"/>
+        <v>8.16260460702334E-3</v>
+      </c>
+    </row>
+    <row r="87" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E87">
+        <f t="shared" si="7"/>
+        <v>1.3611578110523498E-2</v>
+      </c>
+    </row>
+    <row r="88" spans="5:5" x14ac:dyDescent="0.3">
+      <c r="E88">
+        <f t="shared" si="7"/>
+        <v>4.238756237145419E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="14">
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="C14:E14"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="A14:A15"/>
     <mergeCell ref="A17:A19"/>
     <mergeCell ref="A20:A22"/>
     <mergeCell ref="A26:A29"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="C14:E14"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="A14:A15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/models/Extra/WACC_calculation/calculations_PSCC.xlsx
+++ b/models/Extra/WACC_calculation/calculations_PSCC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\msc-thesis-incomplete-markets-LDES\models\Extra\WACC_calculation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{533B5F09-F0AF-4171-8F1A-137EFBC11A04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C1E1402-2F2E-4524-98AD-0A4631DB0FCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10812" yWindow="0" windowWidth="12324" windowHeight="12336" xr2:uid="{96383EBD-4DDB-4AF0-82D8-D5946F1DED23}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{96383EBD-4DDB-4AF0-82D8-D5946F1DED23}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="27">
   <si>
     <t>Storage Duration</t>
   </si>
@@ -105,6 +105,18 @@
   </si>
   <si>
     <t>sw</t>
+  </si>
+  <si>
+    <t>SW</t>
+  </si>
+  <si>
+    <t>SW Complete</t>
+  </si>
+  <si>
+    <t>SW Incomplete</t>
+  </si>
+  <si>
+    <t>total costs</t>
   </si>
 </sst>
 </file>
@@ -113,7 +125,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="174" formatCode="0.000000000"/>
+    <numFmt numFmtId="165" formatCode="0.000000000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -185,6 +197,22 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
@@ -206,22 +234,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,7 +617,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6432F40-47FA-41FE-B3BA-B8FF160E7C28}">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:V88"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="9.5546875" bestFit="1" customWidth="1"/>
@@ -614,6 +626,11 @@
     <col min="6" max="6" width="31.5546875" customWidth="1"/>
     <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -768,36 +785,36 @@
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
-      <c r="B14" s="19" t="s">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18" t="s">
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="20"/>
-      <c r="B15" s="20"/>
+      <c r="A15" s="16"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
@@ -844,7 +861,7 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B17" s="8">
@@ -872,7 +889,7 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="12"/>
+      <c r="A18" s="18"/>
       <c r="B18" s="9">
         <v>0.5</v>
       </c>
@@ -898,7 +915,7 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="13"/>
+      <c r="A19" s="19"/>
       <c r="B19" s="10">
         <v>0.25</v>
       </c>
@@ -924,7 +941,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="8">
         <v>0.75</v>
       </c>
@@ -950,7 +967,7 @@
       </c>
     </row>
     <row r="21" spans="1:8" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="12"/>
+      <c r="A21" s="18"/>
       <c r="B21" s="9">
         <v>0.5</v>
       </c>
@@ -976,7 +993,7 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13"/>
+      <c r="A22" s="19"/>
       <c r="B22" s="10">
         <v>0.25</v>
       </c>
@@ -1002,14 +1019,14 @@
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
+      <c r="A25" s="23"/>
+      <c r="B25" s="23"/>
       <c r="C25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" s="20" t="s">
         <v>12</v>
       </c>
       <c r="B26" s="3" t="s">
@@ -1020,7 +1037,7 @@
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="15"/>
+      <c r="A27" s="21"/>
       <c r="B27" t="s">
         <v>9</v>
       </c>
@@ -1029,7 +1046,7 @@
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="15"/>
+      <c r="A28" s="21"/>
       <c r="B28" t="s">
         <v>10</v>
       </c>
@@ -1038,7 +1055,7 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="16"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="1" t="s">
         <v>11</v>
       </c>
@@ -1047,7 +1064,7 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="20" t="s">
         <v>13</v>
       </c>
       <c r="B30" s="3" t="s">
@@ -1058,7 +1075,7 @@
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="15"/>
+      <c r="A31" s="21"/>
       <c r="B31" t="s">
         <v>9</v>
       </c>
@@ -1067,7 +1084,7 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="15"/>
+      <c r="A32" s="21"/>
       <c r="B32" t="s">
         <v>10</v>
       </c>
@@ -1075,8 +1092,8 @@
         <v>7.9</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="16"/>
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A33" s="22"/>
       <c r="B33" s="1" t="s">
         <v>11</v>
       </c>
@@ -1084,8 +1101,8 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A34" s="20" t="s">
         <v>14</v>
       </c>
       <c r="B34" s="3" t="s">
@@ -1095,8 +1112,8 @@
         <v>11.87</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="15"/>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A35" s="21"/>
       <c r="B35" t="s">
         <v>9</v>
       </c>
@@ -1104,8 +1121,8 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="15"/>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A36" s="21"/>
       <c r="B36" t="s">
         <v>10</v>
       </c>
@@ -1113,8 +1130,8 @@
         <v>8.6300000000000008</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="16"/>
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A37" s="22"/>
       <c r="B37" s="1" t="s">
         <v>11</v>
       </c>
@@ -1122,17 +1139,17 @@
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B42" s="22" t="s">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B42" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="22"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B43" s="21" t="s">
+      <c r="C42" s="13"/>
+    </row>
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B43" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D43" t="s">
@@ -1141,8 +1158,14 @@
       <c r="F43" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P43" t="s">
+        <v>23</v>
+      </c>
+      <c r="R43" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>1</v>
       </c>
@@ -1162,25 +1185,49 @@
       <c r="F44">
         <v>10923247265.1402</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B46" s="22" t="s">
+      <c r="P44">
+        <v>10923247265.1402</v>
+      </c>
+      <c r="R44">
+        <f>1153490016.8662/15</f>
+        <v>76899334.45774667</v>
+      </c>
+    </row>
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B46" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="C46" s="22"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B47" s="21" t="s">
+      <c r="C46" s="13"/>
+      <c r="P46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B47" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D47" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="N47">
+        <v>150040.54599952599</v>
+      </c>
+      <c r="O47">
+        <f>P47-P58</f>
+        <v>150040.54599952698</v>
+      </c>
+      <c r="P47">
+        <v>10923270565</v>
+      </c>
+      <c r="Q47" s="9">
+        <f>100*(P47-$P$44)/$R$44</f>
+        <v>3.0299169641242022E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>0.9</v>
       </c>
@@ -1193,8 +1240,33 @@
       <c r="D48">
         <v>10922995152.261499</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E48">
+        <v>11.93</v>
+      </c>
+      <c r="H48">
+        <f>(B48-$B$44)</f>
+        <v>-3.7368999999999915</v>
+      </c>
+      <c r="K48">
+        <f>100*(E48-$C$44)/$C$44</f>
+        <v>-1.5235056216109819</v>
+      </c>
+      <c r="N48">
+        <v>300040.54599952599</v>
+      </c>
+      <c r="O48">
+        <f t="shared" ref="O48:O55" si="3">P48-P59</f>
+        <v>300040.54599952698</v>
+      </c>
+      <c r="P48">
+        <v>10923320565</v>
+      </c>
+      <c r="Q48" s="9">
+        <f>100*(P48-$P$44)/$R$44</f>
+        <v>9.5319238218653637E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>0.8</v>
       </c>
@@ -1207,8 +1279,33 @@
       <c r="D49">
         <v>10922782112.403</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E49">
+        <v>11.55</v>
+      </c>
+      <c r="H49">
+        <f t="shared" ref="H49:H56" si="4">(B49-$B$44)</f>
+        <v>-7.1245999999999867</v>
+      </c>
+      <c r="K49">
+        <f t="shared" ref="K49:K56" si="5">100*(E49-$C$44)/$C$44</f>
+        <v>-4.6602254760776818</v>
+      </c>
+      <c r="N49">
+        <v>477740.43670081999</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="3"/>
+        <v>477740.43670082092</v>
+      </c>
+      <c r="P49">
+        <v>10923379565</v>
+      </c>
+      <c r="Q49" s="9">
+        <f>100*(P49-$P$44)/$R$44</f>
+        <v>0.17204291913999933</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.7</v>
       </c>
@@ -1221,8 +1318,33 @@
       <c r="D50">
         <v>10922560710.6152</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E50">
+        <v>11.16</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="4"/>
+        <v>-10.256200000000007</v>
+      </c>
+      <c r="K50">
+        <f t="shared" si="5"/>
+        <v>-7.8794905898724652</v>
+      </c>
+      <c r="N50">
+        <v>737240.10470008804</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="3"/>
+        <v>737240.1047000885</v>
+      </c>
+      <c r="P50">
+        <v>10923447065</v>
+      </c>
+      <c r="Q50" s="9">
+        <f>100*(P50-$P$44)/$R$44</f>
+        <v>0.25982001171950503</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>0.6</v>
       </c>
@@ -1235,8 +1357,33 @@
       <c r="D51">
         <v>10922302339.0436</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E51">
+        <v>10.99</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="4"/>
+        <v>-13.29379999999999</v>
+      </c>
+      <c r="K51">
+        <f t="shared" si="5"/>
+        <v>-9.2827599984496771</v>
+      </c>
+      <c r="N51">
+        <v>931980.09799957299</v>
+      </c>
+      <c r="O51">
+        <f t="shared" si="3"/>
+        <v>931980.09799957275</v>
+      </c>
+      <c r="P51">
+        <v>10923505657</v>
+      </c>
+      <c r="Q51" s="9">
+        <f>100*(P51-$P$44)/$R$44</f>
+        <v>0.336013128881259</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>0.5</v>
       </c>
@@ -1249,8 +1396,33 @@
       <c r="D52">
         <v>10922081012.8708</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E52">
+        <v>10.85</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="4"/>
+        <v>-16.101299999999995</v>
+      </c>
+      <c r="K52">
+        <f t="shared" si="5"/>
+        <v>-10.438393629042679</v>
+      </c>
+      <c r="N52">
+        <v>1180165.9519958501</v>
+      </c>
+      <c r="O52">
+        <f t="shared" si="3"/>
+        <v>1180165.9519958496</v>
+      </c>
+      <c r="P52">
+        <v>10923599657</v>
+      </c>
+      <c r="Q52" s="9">
+        <f>100*(P52-$P$44)/$R$44</f>
+        <v>0.45825085780679287</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>0.4</v>
       </c>
@@ -1263,8 +1435,33 @@
       <c r="D53">
         <v>10921883049.368</v>
       </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E53">
+        <v>9.9600000000000009</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="4"/>
+        <v>-18.593199999999996</v>
+      </c>
+      <c r="K53">
+        <f t="shared" si="5"/>
+        <v>-17.784921709241011</v>
+      </c>
+      <c r="N53">
+        <v>1551621.4845008799</v>
+      </c>
+      <c r="O53">
+        <f t="shared" si="3"/>
+        <v>1551621.484500885</v>
+      </c>
+      <c r="P53">
+        <v>10923670657</v>
+      </c>
+      <c r="Q53" s="9">
+        <f>100*(P53-$P$44)/$R$44</f>
+        <v>0.5505793551867173</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>0.3</v>
       </c>
@@ -1277,8 +1474,33 @@
       <c r="D54">
         <v>10921628803.5324</v>
       </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E54">
+        <v>9.24</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="4"/>
+        <v>-20.775700000000001</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="5"/>
+        <v>-23.728180380862145</v>
+      </c>
+      <c r="N54">
+        <v>2886826.3337001801</v>
+      </c>
+      <c r="O54">
+        <f t="shared" si="3"/>
+        <v>2886826.3337001801</v>
+      </c>
+      <c r="P54">
+        <v>10923765657</v>
+      </c>
+      <c r="Q54" s="9">
+        <f>100*(P54-$P$44)/$R$44</f>
+        <v>0.67411748548379935</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>0.2</v>
       </c>
@@ -1291,8 +1513,33 @@
       <c r="D55">
         <v>10921355167.3988</v>
       </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E55">
+        <v>8.4</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="4"/>
+        <v>-22.744</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="5"/>
+        <v>-30.661982164420131</v>
+      </c>
+      <c r="N55">
+        <v>4630098.2474994659</v>
+      </c>
+      <c r="O55">
+        <f t="shared" si="3"/>
+        <v>4630098.2474994659</v>
+      </c>
+      <c r="P55">
+        <v>10923885657</v>
+      </c>
+      <c r="Q55" s="9">
+        <f>100*(P55-$P$44)/$R$44</f>
+        <v>0.8301656500695872</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>0.1</v>
       </c>
@@ -1305,25 +1552,73 @@
       <c r="D56">
         <v>10921045378.714899</v>
       </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B58" s="22" t="s">
+      <c r="E56">
+        <v>7.89</v>
+      </c>
+      <c r="F56">
+        <f>100*(C44-E56)/C44</f>
+        <v>34.871790390151773</v>
+      </c>
+      <c r="H56">
+        <f t="shared" si="4"/>
+        <v>-23.947399999999988</v>
+      </c>
+      <c r="K56">
+        <f t="shared" si="5"/>
+        <v>-34.871790390151773</v>
+      </c>
+      <c r="V56" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="P57" t="s">
+        <v>25</v>
+      </c>
+      <c r="V57">
+        <v>10922995152.261499</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B58" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C58" s="22"/>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B59" s="21" t="s">
+      <c r="C58" s="13"/>
+      <c r="P58">
+        <f>P47-N47</f>
+        <v>10923120524.454</v>
+      </c>
+      <c r="Q58" s="9">
+        <f>100*(P58-$P$44)/$R$44</f>
+        <v>-0.16481376216438848</v>
+      </c>
+      <c r="V58">
+        <v>10922782112.403</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="B59" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C59" s="21" t="s">
+      <c r="C59" s="11" t="s">
         <v>20</v>
       </c>
       <c r="D59" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P59">
+        <f t="shared" ref="P59:P66" si="6">P48-N48</f>
+        <v>10923020524.454</v>
+      </c>
+      <c r="Q59" s="9">
+        <f>100*(P59-$P$44)/$R$44</f>
+        <v>-0.29485389931921169</v>
+      </c>
+      <c r="V59">
+        <v>10922560710.6152</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>0.9</v>
       </c>
@@ -1340,12 +1635,31 @@
         <f>C48-C60</f>
         <v>-0.69999999999999929</v>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="12">
         <f>E60*100/$D$44</f>
         <v>-1.2270837175048149E-4</v>
       </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H60">
+        <f>(B60-$B$44)</f>
+        <v>4.6144999999999925</v>
+      </c>
+      <c r="K60">
+        <f>100*(C60-$C$44)/$C$44</f>
+        <v>0.70521638024693878</v>
+      </c>
+      <c r="P60">
+        <f t="shared" si="6"/>
+        <v>10922901824.563299</v>
+      </c>
+      <c r="Q60" s="9">
+        <f>100*(P60-$P$44)/$R$44</f>
+        <v>-0.44921139998979959</v>
+      </c>
+      <c r="V60">
+        <v>10922302339.0436</v>
+      </c>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>0.8</v>
       </c>
@@ -1359,15 +1673,34 @@
         <v>10922863407.857</v>
       </c>
       <c r="E61">
-        <f t="shared" ref="E61:E68" si="3">C49-C61</f>
+        <f t="shared" ref="E61:E68" si="7">C49-C61</f>
         <v>-1.4924230434150996</v>
       </c>
       <c r="F61">
-        <f t="shared" ref="F61:F68" si="4">E61*100/$D$44</f>
+        <f t="shared" ref="F61:F68" si="8">E61*100/$D$44</f>
         <v>-2.6161828802909312E-4</v>
       </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H61">
+        <f t="shared" ref="H61:H68" si="9">(B61-$B$44)</f>
+        <v>9.6888000000000147</v>
+      </c>
+      <c r="K61">
+        <f t="shared" ref="K61:K68" si="10">100*(C61-$C$44)/$C$44</f>
+        <v>1.8987368568311072</v>
+      </c>
+      <c r="P61">
+        <f t="shared" si="6"/>
+        <v>10922709824.8953</v>
+      </c>
+      <c r="Q61" s="9">
+        <f>100*(P61-$P$44)/$R$44</f>
+        <v>-0.6988880315928524</v>
+      </c>
+      <c r="V61">
+        <v>10922081012.8708</v>
+      </c>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>0.7</v>
       </c>
@@ -1381,15 +1714,34 @@
         <v>10922574936.178499</v>
       </c>
       <c r="E62">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-1.8815463715626013</v>
       </c>
       <c r="F62">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-3.2983070232496211E-4</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H62">
+        <f t="shared" si="9"/>
+        <v>15.202400000000011</v>
+      </c>
+      <c r="K62">
+        <f t="shared" si="10"/>
+        <v>6.3289015564006306</v>
+      </c>
+      <c r="P62">
+        <f t="shared" si="6"/>
+        <v>10922573676.902</v>
+      </c>
+      <c r="Q62" s="9">
+        <f>100*(P62-$P$44)/$R$44</f>
+        <v>-0.87593506881304117</v>
+      </c>
+      <c r="V62">
+        <v>10921883049.368</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>0.6</v>
       </c>
@@ -1403,15 +1755,34 @@
         <v>10922238614.9389</v>
       </c>
       <c r="E63">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-2.2669324105457989</v>
       </c>
       <c r="F63">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-3.9738797852352753E-4</v>
       </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H63">
+        <f t="shared" si="9"/>
+        <v>21.461200000000019</v>
+      </c>
+      <c r="K63">
+        <f t="shared" si="10"/>
+        <v>10.855734642734319</v>
+      </c>
+      <c r="P63">
+        <f t="shared" si="6"/>
+        <v>10922419491.048004</v>
+      </c>
+      <c r="Q63" s="9">
+        <f>100*(P63-$P$44)/$R$44</f>
+        <v>-1.0764385648231352</v>
+      </c>
+      <c r="V63">
+        <v>10921628803.5324</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>0.5</v>
       </c>
@@ -1425,15 +1796,34 @@
         <v>10921849032.7728</v>
       </c>
       <c r="E64">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-4.1643775130476985</v>
       </c>
       <c r="F64">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-7.3000569140057583E-4</v>
       </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H64">
+        <f t="shared" si="9"/>
+        <v>29.088600000000014</v>
+      </c>
+      <c r="K64">
+        <f t="shared" si="10"/>
+        <v>32.896661953370128</v>
+      </c>
+      <c r="P64">
+        <f t="shared" si="6"/>
+        <v>10922119035.515499</v>
+      </c>
+      <c r="Q64" s="9">
+        <f>100*(P64-$P$44)/$R$44</f>
+        <v>-1.4671513513819376</v>
+      </c>
+      <c r="V64">
+        <v>10921355167.3988</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>0.4</v>
       </c>
@@ -1447,15 +1837,34 @@
         <v>10921849032.7728</v>
       </c>
       <c r="E65">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-5.1558582983203998</v>
       </c>
       <c r="F65">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-9.0380996680443587E-4</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H65">
+        <f t="shared" si="9"/>
+        <v>40.855199999999996</v>
+      </c>
+      <c r="K65">
+        <f t="shared" si="10"/>
+        <v>37.91303061438559</v>
+      </c>
+      <c r="P65">
+        <f t="shared" si="6"/>
+        <v>10920878830.6663</v>
+      </c>
+      <c r="Q65" s="9">
+        <f>100*(P65-$P$44)/$R$44</f>
+        <v>-3.0799154382814695</v>
+      </c>
+      <c r="V65">
+        <v>10921045378.714899</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>0.3</v>
       </c>
@@ -1469,15 +1878,31 @@
         <v>10920737182.047899</v>
       </c>
       <c r="E66">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-5.4728070330901009</v>
       </c>
       <c r="F66">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-9.5937034276438618E-4</v>
       </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H66">
+        <f t="shared" si="9"/>
+        <v>59.398500000000013</v>
+      </c>
+      <c r="K66">
+        <f t="shared" si="10"/>
+        <v>53.881707793432874</v>
+      </c>
+      <c r="P66">
+        <f t="shared" si="6"/>
+        <v>10919255558.752501</v>
+      </c>
+      <c r="Q66" s="9">
+        <f>100*(P66-$P$44)/$R$44</f>
+        <v>-5.1908204613817848</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>0.2</v>
       </c>
@@ -1491,15 +1916,23 @@
         <v>10919868341.0651</v>
       </c>
       <c r="E67">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-5.6999332726029994</v>
       </c>
       <c r="F67">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-9.9918504423929721E-4</v>
       </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H67">
+        <f t="shared" si="9"/>
+        <v>83.799300000000017</v>
+      </c>
+      <c r="K67">
+        <f t="shared" si="10"/>
+        <v>78.389147257196683</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>0.1</v>
       </c>
@@ -1513,15 +1946,31 @@
         <v>10916415280.4674</v>
       </c>
       <c r="E68">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>-17.812128038380404</v>
       </c>
       <c r="F68">
-        <f t="shared" si="4"/>
+        <f t="shared" si="8"/>
         <v>-3.1224246128582277E-3</v>
       </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H68">
+        <f t="shared" si="9"/>
+        <v>166.08359999999999</v>
+      </c>
+      <c r="K68">
+        <f t="shared" si="10"/>
+        <v>217.8293847507824</v>
+      </c>
+      <c r="V68" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="V69">
+        <v>10923116520.682899</v>
+      </c>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D70">
         <f>D48-D60</f>
         <v>-121368.42140007019</v>
@@ -1534,10 +1983,16 @@
         <f>E60*100/$C$44</f>
         <v>-5.7781681529649829</v>
       </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P70">
+        <v>-5.1908204613817848</v>
+      </c>
+      <c r="V70">
+        <v>10922863407.857</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D71">
-        <f>D49-D61</f>
+        <f t="shared" ref="D71:D78" si="11">D49-D61</f>
         <v>-81295.454000473022</v>
       </c>
       <c r="E71" s="9">
@@ -1545,13 +2000,19 @@
         <v>8704.5459995269775</v>
       </c>
       <c r="F71">
-        <f t="shared" ref="F71:F79" si="5">E61*100/$C$44</f>
+        <f t="shared" ref="F71:F78" si="12">E61*100/$C$44</f>
         <v>-12.319244714588876</v>
       </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P71">
+        <v>-3.0799154382814695</v>
+      </c>
+      <c r="V71">
+        <v>10922574936.178499</v>
+      </c>
+    </row>
+    <row r="72" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D72">
-        <f>D50-D62</f>
+        <f t="shared" si="11"/>
         <v>-14225.563299179077</v>
       </c>
       <c r="E72" s="9">
@@ -1559,41 +2020,59 @@
         <v>25774.436700820923</v>
       </c>
       <c r="F72">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-15.531273317842645</v>
       </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P72">
+        <v>-1.4671513513819376</v>
+      </c>
+      <c r="V72">
+        <v>10922238614.9389</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D73">
-        <f>D51-D63</f>
+        <f t="shared" si="11"/>
         <v>63724.104700088501</v>
       </c>
       <c r="E73" s="9">
-        <f t="shared" ref="E71:E78" si="6">D73</f>
+        <f t="shared" ref="E73:E78" si="13">D73</f>
         <v>63724.104700088501</v>
       </c>
       <c r="F73">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-18.712452370771267</v>
       </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P73">
+        <v>-1.0764385648231352</v>
+      </c>
+      <c r="V73">
+        <v>10921849032.7728</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D74">
-        <f>D52-D64</f>
+        <f t="shared" si="11"/>
         <v>231980.09799957275</v>
       </c>
       <c r="E74" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>231980.09799957275</v>
       </c>
       <c r="F74">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-34.374962175451074</v>
       </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P74">
+        <v>-0.87593506881304117</v>
+      </c>
+      <c r="V74">
+        <v>10921849032.7728</v>
+      </c>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D75">
-        <f>D53-D65</f>
+        <f t="shared" si="11"/>
         <v>34016.595199584961</v>
       </c>
       <c r="E75" s="9">
@@ -1601,53 +2080,74 @@
         <v>340165.95199584961</v>
       </c>
       <c r="F75">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-42.559166029364562</v>
       </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P75">
+        <v>-0.6988880315928524</v>
+      </c>
+      <c r="V75">
+        <v>10920737182.047899</v>
+      </c>
+    </row>
+    <row r="76" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D76">
-        <f>D54-D66</f>
+        <f t="shared" si="11"/>
         <v>891621.48450088501</v>
       </c>
       <c r="E76" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>891621.48450088501</v>
       </c>
       <c r="F76">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-45.175427579891462</v>
       </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P76">
+        <v>-0.44921139998979959</v>
+      </c>
+      <c r="V76">
+        <v>10919868341.0651</v>
+      </c>
+    </row>
+    <row r="77" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D77">
-        <f>D55-D67</f>
+        <f t="shared" si="11"/>
         <v>1486826.3337001801</v>
       </c>
       <c r="E77" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>1486826.3337001801</v>
       </c>
       <c r="F77">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-47.050247013971649</v>
       </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P77">
+        <v>-0.29485389931921169</v>
+      </c>
+      <c r="V77">
+        <v>10916415280.4674</v>
+      </c>
+    </row>
+    <row r="78" spans="1:22" x14ac:dyDescent="0.3">
       <c r="D78">
-        <f>D56-D68</f>
+        <f t="shared" si="11"/>
         <v>4630098.2474994659</v>
       </c>
       <c r="E78" s="9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>4630098.2474994659</v>
       </c>
       <c r="F78">
-        <f t="shared" si="5"/>
+        <f t="shared" si="12"/>
         <v>-147.03067281129196</v>
       </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="P78">
+        <v>-0.16481376216438848</v>
+      </c>
+    </row>
+    <row r="80" spans="1:22" x14ac:dyDescent="0.3">
       <c r="E80">
         <f>E70*100/$F$44</f>
         <v>1.03593608426412E-5</v>
@@ -1655,53 +2155,56 @@
     </row>
     <row r="81" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E81">
-        <f t="shared" ref="E81:E89" si="7">E71*100/$F$44</f>
+        <f t="shared" ref="E81:E88" si="14">E71*100/$F$44</f>
         <v>7.9688262915242678E-5</v>
       </c>
     </row>
     <row r="82" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E82">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>2.3595947317860252E-4</v>
       </c>
     </row>
     <row r="83" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E83">
-        <f t="shared" si="7"/>
+        <f>E73*100/$F$44</f>
         <v>5.8338059327333745E-4</v>
       </c>
     </row>
     <row r="84" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E84">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>2.1237283416617346E-3</v>
       </c>
     </row>
     <row r="85" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E85">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>3.114146771001284E-3</v>
       </c>
     </row>
     <row r="86" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E86">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>8.16260460702334E-3</v>
       </c>
     </row>
     <row r="87" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E87">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>1.3611578110523498E-2</v>
       </c>
     </row>
     <row r="88" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E88">
-        <f t="shared" si="7"/>
+        <f t="shared" si="14"/>
         <v>4.238756237145419E-2</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="P70:P78">
+    <sortCondition ref="P70:P78"/>
+  </sortState>
   <mergeCells count="14">
     <mergeCell ref="B58:C58"/>
     <mergeCell ref="B46:C46"/>
@@ -1719,6 +2222,7 @@
     <mergeCell ref="A25:B25"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>